--- a/storage/app/DWR.xlsx
+++ b/storage/app/DWR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="61">
   <si>
     <t>Report Date</t>
   </si>
@@ -63,6 +63,141 @@
   </si>
   <si>
     <t>working days</t>
+  </si>
+  <si>
+    <t>Sirte Oil Company</t>
+  </si>
+  <si>
+    <t>S.ZELTEN</t>
+  </si>
+  <si>
+    <t>C163-6</t>
+  </si>
+  <si>
+    <t>NWD#36</t>
+  </si>
+  <si>
+    <t>R/D 100%, R/M 0% &amp; R/U 0%. PREPARE TO MOVE CAMP.</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>N.ZELTEN</t>
+  </si>
+  <si>
+    <t>C199-6</t>
+  </si>
+  <si>
+    <t>LORASCO #25</t>
+  </si>
+  <si>
+    <t>CONT POOH W/ 6 1/8’’ BIT &amp; 7’’ CSG SCRAPER F/ 700’ T/ SURFACE &amp; L/D SAME, R/U TAQA WL, RUN GR-CCL CORRELATION LOG, TAG PBTD @ 5592’, POOH &amp; R/D WL TOOLS, M/U &amp; RIH W/ 6 1/8&amp;#039;&amp;#039; BIT ON 3 1/2&amp;#039;&amp;#039; DP F/ SURFACE, TAG @ 5600&amp;#039; (D.DEPTH), D.O.C F/ 5600&amp;#039; T/ 5639&amp;#039; (NEW PBTD), SWEEP &amp; CIRCULATE HOLE CLEAN, POOH W/ 6 1/8’’ BIT T/ 4850’ @ RT.</t>
+  </si>
+  <si>
+    <t>C179-6</t>
+  </si>
+  <si>
+    <t>ADWOC # 8</t>
+  </si>
+  <si>
+    <t>R/D 100%, R/M 100% &amp; R/U 65%.  CONT WORKING ON LEVELING LOCATION</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>JEBEL</t>
+  </si>
+  <si>
+    <t>P10-6</t>
+  </si>
+  <si>
+    <t>CHALL# 96</t>
+  </si>
+  <si>
+    <t>INFIELD MOBILIZATION. R/D :100%, R//M: 100%, R/U: 40%</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>C109-6</t>
+  </si>
+  <si>
+    <t>ADWOC# 5</t>
+  </si>
+  <si>
+    <t>INTERFIELD MOBILIZATION FROM RAGUBA TO ZELTEN. R/D: 100%, R/M: 5%, R/UP: 0%. WAITING FOR KEENWORTH</t>
+  </si>
+  <si>
+    <t>ARSHAD</t>
+  </si>
+  <si>
+    <t>MMM10-6</t>
+  </si>
+  <si>
+    <t>Q.B# 8</t>
+  </si>
+  <si>
+    <t>RIG UP TEST SEPARATOR AND SURFACE LINE, START UP ESP FOR CLEAN UP, LAST READINGS @ 23:00 HRS: FWHP= 20 PSI, CP= 0 PSI, WC= 85%, SAL= 1000 PPM, FRQ= 57 HTZ, CK= 24/64&amp;#039;&amp;#039;, Pi= 744 PSI, SWITCH OFF ESP, SHUT-IN WELL FOR PRESSURE BUILD UP, AT 5:00 HRS: SIWHP= 150 PSI, Pi= 1164 PSI, Pd=: 1169 PSI, Ti= 270⁰, Tm=270⁰.</t>
+  </si>
+  <si>
+    <t>C126-6</t>
+  </si>
+  <si>
+    <t>ADWOC#22</t>
+  </si>
+  <si>
+    <t>RIG DOWN: 100%, RIG MOVE: 100%, RIG UP: 0%.</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>C108-6</t>
+  </si>
+  <si>
+    <t>NWD#53</t>
+  </si>
+  <si>
+    <t>R/U SLB WL EQUIPT, RUN 3 ½” HSD GUN (6 SPF) W/ CCL-GR LOG, CORRELATE DEPTH AND PERFORATE 10’ OH INTERVAL F/ 5600’ T/ 5610’ ACROSS ZELTEN POROSITY PAYZONE, POOH &amp; L/D WL TOOLS, CHECK GUN (ALL SHOTS FIRED), M/U &amp; RIH W/ 2 3/8” FINAL GAS-LIFT COMPLETION T/ 3156’ @ R/TIME.</t>
+  </si>
+  <si>
+    <t>WADI</t>
+  </si>
+  <si>
+    <t>D7-NC149</t>
+  </si>
+  <si>
+    <t>LAHEEB#1</t>
+  </si>
+  <si>
+    <t>R/UP 100%, RIG ON PAYROLL ON 14/7/2026 @ 05:00 HRS, SICP: 150 PSI, SITP: 200 PSI, BLEED OFF BOTH T/ 0 PSI, KILL WELL, N/D X-MASS TREE, N/U &amp; TEST BOP’S OK, POOH W/ ESP ON 105 STDS  2 7/8&amp;#039;&amp;#039; TBG F/ 7821&amp;#039; T/ 1416&amp;#039; @ RT</t>
+  </si>
+  <si>
+    <t>A3-LP3D</t>
+  </si>
+  <si>
+    <t>FB#7</t>
+  </si>
+  <si>
+    <t>MADE NEW LOWER PIGTAIL SPLICE, LAND TBG HGR (INTAKE @ 6945’, C.V @ 6802’, B.V @ 6782&amp;#039;), N/D BOP’S, N/U &amp; P/T X-MASS TREE T/ 2000 PSI-OK, SPOT &amp; R/U TEST SEPARATOR, START UP ESP, FLOW WELL FOR CLEAN UP ON 32/64” CHK, FWHP= 310 PSI, CSG P= 0 PSI, W.C= 92%.      SAL= 2000 PPM, FRQ= 50 HTZ, Pi= 2106 PSI, Pd= 2979 PSI, Tm= 246⁰ F, Ti= 230⁰ F, AMPS: 15.6 A.</t>
+  </si>
+  <si>
+    <t>RAGUBA</t>
+  </si>
+  <si>
+    <t>E56-20</t>
+  </si>
+  <si>
+    <t>NDD#4</t>
+  </si>
+  <si>
+    <t>INFIELD MOBILIZATION. R/D 100%, R/M 100%, R/U 90%</t>
+  </si>
+  <si>
+    <t>C</t>
   </si>
 </sst>
 </file>
@@ -527,7 +662,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="true" style="9"/>
@@ -621,6 +756,378 @@
       </c>
       <c r="M2" s="15"/>
     </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10">
+        <v>561</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
+        <v>0</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="L3" s="17" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="10">
+        <v>561</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="11"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
+        <v>0</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="L4" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10">
+        <v>561</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="11"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="13">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
+        <v>0</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="L5" s="17" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="10">
+        <v>561</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G6" s="11"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>0</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10">
+        <v>561</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="11"/>
+      <c r="H7" s="19"/>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>0</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="L7" s="17" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10">
+        <v>561</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="11"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>41</v>
+      </c>
+      <c r="L8" s="17">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10">
+        <v>561</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="G9" s="11"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
+        <v>0</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="L9" s="17" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="10">
+        <v>561</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="G10" s="11"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>0</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="L10" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="10">
+        <v>561</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>49</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G11" s="11"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="13">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13">
+        <v>0</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L11" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="10">
+        <v>561</v>
+      </c>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="G12" s="11"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
+        <v>0</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="L12" s="17">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="18">
+        <v>46218.0</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="10">
+        <v>561</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G13" s="11"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>0</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="17" t="s">
+        <v>60</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/storage/app/DWR.xlsx
+++ b/storage/app/DWR.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="205">
   <si>
     <t>Report Date</t>
   </si>
@@ -63,6 +63,573 @@
   </si>
   <si>
     <t>working days</t>
+  </si>
+  <si>
+    <t>AGOCO</t>
+  </si>
+  <si>
+    <t>DOR-MANSOUR</t>
+  </si>
+  <si>
+    <t>A1-104</t>
+  </si>
+  <si>
+    <t>ADC#050</t>
+  </si>
+  <si>
+    <t>WORKOVER</t>
+  </si>
+  <si>
+    <t>CONT RIG UP, R/UP: 100 %, N/D PROD-LOOP &amp; P/T TBG UP TO 500 PSI X 15 MINs \"GOOD TEST\", DROP BAR &amp; KILL THE WELL REVs-CIR'C BY PUMPING 10 BBL H2O 8.4 PPG &amp; PUMPING D/ TBG 10 BBL H2O 8.4 PPG, OBSERVE WELL, WELL STATIC, STRIP OUT HER'C FLANGE &amp; STRIP IN 7 1/16\" BOPs, F/T BOPs \"OK\", R/UP WORK FLOOR, CAT WALK, V-DOOR + PIPE RACKs &amp; TBG EQUIP, P/UP &amp; RIH W/ ESP UNIT ON 3 JTs 3 1/2\" TBG BURY CABLE.</t>
+  </si>
+  <si>
+    <t>HAMADA</t>
+  </si>
+  <si>
+    <t>AA1-NC8</t>
+  </si>
+  <si>
+    <t>ENTISAR#003</t>
+  </si>
+  <si>
+    <t>MAJOR WORKOVER</t>
+  </si>
+  <si>
+    <t>CONT RIH W/ 4 3/4\" BIT + 5 1/2\" CSG SCR ON 152 JTS 2 7/8\" TBG, P/UP 1 JOINT TAG @ 4838' (2' FILL), R/UP FLOW LINES + CIRC. LINE &amp; CIRCULATE HOLE &amp; CLEAN UP WELL W/ 90 BBLs H?O TO DBP @4840', L/D 1 JOINT 2 7/8\" TBG &amp; POOH W/ 4 3/4\" BIT + 5 1/2\" CSG SCR ON TOTAL OF 152 JTS 27/8\"TBG SET BACK AT DRK, P/UP, M/UP &amp; RIH W/ 5 1/2\" D&amp;L AGOCO PKR ON TOTAL OF 152 JTS 3 1/2\" TBG SET PKR @ 4823', R/UP CIRC. LINES, FILL UP WELL 4840' TO 4823' &amp; TBG TILL SPILL POINT BY H?O W/ 90 BBLs &amp; START P/TEST DBP @ 4840' TO 500 PSI FOR 15 MINTS -NO TEST ATTEMPT TO RE- TEST FOR 3 TIMES - NO SUCCESS PRESS. DROP, TO ZERO IN 2.5 MINTS, UN-SET PKR &amp; P/UP 1 PUP JOINT 10' 2 7/8\" TBG &amp; SET PKR @ 4832', R/UP CIRC. LINES &amp; P/D TUBING W/ 10 BBLs H?O, P/T DBP TO 500 PSI FOR 15 MINS - NO TEST PRESS. DROP TO ZERO IN 1.5 MINTS, ATTEMPT TO RE-START TEST, NO SUCCESS (SAME RESULT), R/UP X-TREE SWAB + LUBRICATOR &amp; SWAB HEAD, START SWABBING ON DBP - I.F.L = 600', F.F.L = 2200' . MADE 5 SWAB RUNS . RECOVERY 15 BBLS . W.RATIO =100% .</t>
+  </si>
+  <si>
+    <t>I2-NC8</t>
+  </si>
+  <si>
+    <t>ENTISAR#007</t>
+  </si>
+  <si>
+    <t>WAIT ON DAY LIGHT, CONT. SWAB WELL INTERVAL (5142'-5154') TO FLARE PIT, IFL:100', FFL:1200', MADE: 49 S.RUN, RECV:99 BBLS, LAST SAMPLE OIL= 2%, W.C= 98%, WWT= 8.4 PPG, R/D SWAB EQUIP.+ SWAB TREE, UNSET PKR &amp; POOH 1 JT L/D SAME, CONT POOH W/ 5 1/2\" PKR + 34 STDS 2 7/8\" TBG.</t>
+  </si>
+  <si>
+    <t>G1-NC2</t>
+  </si>
+  <si>
+    <t>ILL#005</t>
+  </si>
+  <si>
+    <t>CONT POOH W/ 7\" OIL SERV PKR ON 3 1/2\" TBG OF TOTAL 276 JTS + L/D SAME, P/U + M/U OIL SERV 7\" C.R + 7\" MST AND RIH WITH SAME ON 31/2\" TBG - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>F1-NC2</t>
+  </si>
+  <si>
+    <t>ILL#006</t>
+  </si>
+  <si>
+    <t>POOH + L/D 15 JTS 3 1/2\" TBG KILL STRING, WORK AND MODIFICATION NEW FLOW NIPPLE + FLOW LINE + N/UP SAME, RACK + REMOVE PROTECTOR + SLM 8 JTS 4 3/4\" D.C + 60 JTS 3 1/2\" TBG, P/UP + M/UP 8 1/2\" BIT + BIT SUB + 8 JTS 4 3/4\" D.C + X.O &amp; RIH W/ SAME FROM PIPE RACK, ON 3 1/2\" TBG TOTAL OF 40 JTS - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>G2-NC2</t>
+  </si>
+  <si>
+    <t>NWD#033</t>
+  </si>
+  <si>
+    <t>RIH W/ 2 JTs 3 1/2\" TBG &amp; R/UP POWER SWIVEL, MIX 15 BBLs HI-VIS, BREAK CIRC AND DRILL OUT CMT FROM 7595 FT TO 7653 FT, W.O.B = 4000 LB-5000 LB, 75 - 90 RPM, 3.5 BBLs/MIN, CMT AT SURFACE, PUMP 15 BBLS HI-VIS AND CIRC.HOLE CLEAN W/ 500 BBLS H2O, R/D POWER SWIVEL AND POOH W/ 2 JTs 3 1/2\" TBG.</t>
+  </si>
+  <si>
+    <t>KOTLA</t>
+  </si>
+  <si>
+    <t>C70HRST1-47</t>
+  </si>
+  <si>
+    <t>ADC#018</t>
+  </si>
+  <si>
+    <t>RECOMPLETION</t>
+  </si>
+  <si>
+    <t>R/D PORTABLE SEPARATOR (ABCO COMPANY), P/UP, M/UP SONOLOG EQUIP &amp; MAKE SHOT FOR CHECK FLUID LEVEL, FL @ 2520 FT, START UP ESP UNIT &amp; CONT PUMP WELL TO FLARE PIT FOR TEST; FLOW RATE PUMP= 900 BPD, W.C= 0%, W.H.P= 480 PSI, CHOKE SIZE; 24/64\", SWITCH OFF PUMP @ 20:00 HRS.</t>
+  </si>
+  <si>
+    <t>MAGID</t>
+  </si>
+  <si>
+    <t>O6-80</t>
+  </si>
+  <si>
+    <t>ANCO#007</t>
+  </si>
+  <si>
+    <t>MOVE RIG &amp; RIG EQUIPMENT FROM WELL O7-80 TO WELL O6-80 (3 KM ONE WAY), R/M: 30 %, R/UP: 0 %.</t>
+  </si>
+  <si>
+    <t>O7-80</t>
+  </si>
+  <si>
+    <t>RIG DOWN RIG &amp; RIG EQUIPMENTS, 100 % R/D, MOVE OUT CLEAN LOCATION: 100%, RIG RELEASED @ 14:00 HR TO MOVE TO WELL O6-80.</t>
+  </si>
+  <si>
+    <t>A5HR-105</t>
+  </si>
+  <si>
+    <t>UWD#108</t>
+  </si>
+  <si>
+    <t>POOH W/ O.E.T ON 10 JTS 3 1/2'' TBG, HANG UP 11'' BOP, DISCONNECTED MUD CROSS, STRIP IN C- SECTION &amp;, RE INSTALL 11'' BOP, LOAD 7'' PRODUCTION PKR ON CAT WALK &amp; TAKE MEASUREMENT + I.D + O.D, P/U &amp; M/U X.O 2 7/8'' PIN * 3 1/2'' PIN + COLLAR 4 1/2'' +7'' PRODUCTION PKR &amp; RIH W/ SAME ON 200 JTS 3 1/2'' TBG.</t>
+  </si>
+  <si>
+    <t>MESSLA</t>
+  </si>
+  <si>
+    <t>VV3-65</t>
+  </si>
+  <si>
+    <t>ABCO#011</t>
+  </si>
+  <si>
+    <t>POOH W/ ESP UNIT ON 10 JTS 3 1/2'' TBG AS KILL STRING, DISCONNECTED ESP CABLE &amp; DISMANTLE ESP UNIT + 7'' SHROUDED &amp; L/D SAME, PUT IT BACK IN BOXES, P/U 6 1/8'' BIT + 7'' CSG SCR ON 98 JTS 3 1/2'' TBG W/ ( S.L.M. + DRIFT ) &amp; P/T EVREY, 1000 FT TO 500 PSI FOR 15 MIN GOOD TEST. ( WHILE DRIFT TBG, L/D 16 JT'S BAD TBG).</t>
+  </si>
+  <si>
+    <t>DD27HR-80</t>
+  </si>
+  <si>
+    <t>ABCO#012</t>
+  </si>
+  <si>
+    <t>WAIT ON ESP TECH, SLIP 20' DRILLING LINE, MAKE LOWER PIG TAIL TO MAIN CABLE SPLICE, LAND 9'' TBG HANGER W/ PUMP SUCTION@ 7199' FT &amp; E.O.M @ 7219' FT, N/D 11'' BOP &amp; N/UP W.H.</t>
+  </si>
+  <si>
+    <t>HH56-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2022</t>
+  </si>
+  <si>
+    <t>CONT. R/M F/ C101-65 &amp; R/UP ON HH-56-65, 100% R/M &amp; 75% R/UP.</t>
+  </si>
+  <si>
+    <t>HH88-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2027</t>
+  </si>
+  <si>
+    <t>START R/M F/ HH-33-65 &amp; R/UP ON HH-88-65, 20% R/M &amp; 10% R/UP.</t>
+  </si>
+  <si>
+    <t>DD15-80</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2031</t>
+  </si>
+  <si>
+    <t>CONT. R/UP ON DD15-65, 98% R/UP.</t>
+  </si>
+  <si>
+    <t>DD43-80</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2032</t>
+  </si>
+  <si>
+    <t>CONT. R/UP ON DD43-65, 98% R/UP.</t>
+  </si>
+  <si>
+    <t>NAFOORA AU</t>
+  </si>
+  <si>
+    <t>G327D-91</t>
+  </si>
+  <si>
+    <t>ABCO#005</t>
+  </si>
+  <si>
+    <t>CONT RIH W/ ESP UNIT ON TOTAL 262 JTS 3 1/2'' TBG &amp; P/UP F/ PIPE RACK 1 JT 3 1/2'' TBG W/ TBG HANGER, NO ENOUGH TIME TO CUT &amp; SPLICE CABLE.</t>
+  </si>
+  <si>
+    <t>G259-91</t>
+  </si>
+  <si>
+    <t>ABCO#007</t>
+  </si>
+  <si>
+    <t>RECEIVED ESP PARTS FROM MESSLA FIELD, PREPARATION TO RIH W/ESP, ASSEMBLE ESP UNIT.</t>
+  </si>
+  <si>
+    <t>G326D-51</t>
+  </si>
+  <si>
+    <t>ANCO#002</t>
+  </si>
+  <si>
+    <t>CONT R.I.H W/ 6'' BIT + (6 X 4 3/4'' D.C + X.O.) ON 260 JTS 3 1/2'' TBG W/DRIFT + S.L.M - INCOMPLETE, P/UP + M/UP 3 1/2'' TBG F.PIP RACKs &amp; CONT R.I.H W/ 6'' BIT + B.H.A SINGLE BY SINGLE ON TOTAL OF 279 JTS 3 1/2'' TBG W/ DRIFT + S.L.M - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>G87-91</t>
+  </si>
+  <si>
+    <t>ANCO#003</t>
+  </si>
+  <si>
+    <t>SHUT DOWN DUE TO RIG REPAIR MALFUNCTION IN RIG ENGINE.</t>
+  </si>
+  <si>
+    <t>D43H-91</t>
+  </si>
+  <si>
+    <t>ANCO#004</t>
+  </si>
+  <si>
+    <t>PREPARE 64 JTS 3 1/2\" DP ON PIPE RACK, CLEAN &amp; S.L.M, CONT P/ UP &amp; RIH W/ 6\" BIT+ BHA (6\" BIT + 4' BIT SUB + 46 JTS 3 1/2\" DP + 6 JTS 3 1/2\" HWDP+ 4 3/4\" D.JAR + 7 JTS 3 1/2\" HWDP) ON 172 JTS X 3 1/2\" D.P W/DRIFT - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>G68-91</t>
+  </si>
+  <si>
+    <t>ANCO#006</t>
+  </si>
+  <si>
+    <t>CONT POOH W/ ESP ON TOTAL 224 JTS 3 1/2\" TBG &amp; L/D . (JT BY JT HARD CONNECTION) - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>G242-91</t>
+  </si>
+  <si>
+    <t>AZCO#503</t>
+  </si>
+  <si>
+    <t>CONT TEST E.S.P UNIT, WELL FLOW TO STATION W/ CHOKE SIZE 32/64'', W.H.P= 200 PSI, R/UP NESR SEPARATOR, DIVERT FLOW THROUGH SEPARETOR TO STATION, CHOKE SIZE= 24/64\". W.H.P= 260 PSI, OIL.R= 126 BPD, W.R= 880 BPD, GOR=76 SCF/STB, W.C= 87%, SAL= 40,000 PPM, DIVERT FLOW OVER NIGHT BYPASS NESR SEPARATOR TO STATION W/ CHOKE SIZE 24/64'', W.H.P= 260 PSI.</t>
+  </si>
+  <si>
+    <t>G319D-91</t>
+  </si>
+  <si>
+    <t>UWD#107</t>
+  </si>
+  <si>
+    <t>CONT POOH W / BHA ON 58 JTS 3 1/2'', &amp; L/D BHA W / SAME, SPLICE CABLE, ASSEMBLY ESP UNIT &amp; CONNECT CABLE TO POT HEAD, RIH W / ESP UNIT + C.V &amp; B.V ON 36 JTS 3 1/2'' TBG W / PRESS TEST - GOOD.</t>
+  </si>
+  <si>
+    <t>NAFOORA NNU</t>
+  </si>
+  <si>
+    <t>G308-51</t>
+  </si>
+  <si>
+    <t>ABCO#006</t>
+  </si>
+  <si>
+    <t>POOH W/ 10 JTS 3 1/2'' TBG KILL STRING, P/UP, M/UP 5 3/4'' POOR BOY + BHA ON 324 JTS 3 1/2'' TAG TOP OF FISH @ 10249.5' WORK ON POOR BOY, ENGAGE SWALLOW 10.5' F/T.O.F, APPLY 25000 LB, POOH W/ 5 3/4'' POOR BOY + BHA ON 6 JTS 3 1/2'' TBG, INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>L4-51</t>
+  </si>
+  <si>
+    <t>ANCO#005</t>
+  </si>
+  <si>
+    <t>CONT POOH W/ (6\" BIT + BIT SUB + 6 X 4 3/4\" D.C +X.O) ON TOTAL OF 359 JTS 3 1/2\" TBG STD ON DRK &amp; L/D 6 JTS D.C, P/UP, M/UP 6'' BIT + 7'' SCR &amp; RIH W/ SAME ON 314 JTS 3 1/2'' TBG - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>SARIR</t>
+  </si>
+  <si>
+    <t>L3-65</t>
+  </si>
+  <si>
+    <t>ADC#017</t>
+  </si>
+  <si>
+    <t>CONT WORKING ESP PKR UP &amp; DOWN TO UNSET SAME W/ OVER PULL 65 KLBS NO PROGRESS, ( STRING WEIGHT 75 LBS ) TO SEVERAL TIMES, START REVERSE CIRC W/ PUMP D/CSG/ W/ FULL RETURN TO SYSTEM, CONT WORKING ESP PKR UP &amp; DOWN TO UNSET SAME W/ OVER PULL 65,000 LBS NO PROGRESS, ( STRING WEIGHT 75 LBS ) TO SEVERAL TIMES.</t>
+  </si>
+  <si>
+    <t>C240-65</t>
+  </si>
+  <si>
+    <t>APESCO#015</t>
+  </si>
+  <si>
+    <t>TAG @ 20 FT (5 FT BELOW BOP), PRESSURE TEST TO 500 PSI PRESSURE DROP TO 0 PSI IN 20 SEC, CLEAN INSIDE 34 CSG CONDUCTOR &amp; REMOVE ALL THE IMPURITIES &amp; DRYING THE WATER, MIX CEMENT BY HAND &amp; POURED IT BETWEEN 20'' &amp; 34 CSG CONDUCTOR &amp; ALSO POURED CEMENT INSIDE, CELLAR &amp; AROUND 34'' CONDUCTOR CSG, DISCONNECT 9 5/8'' VALVE CLEANED FROM CEMENT &amp; RE-CONNECT, R/U POWER SWIVEL &amp; PREPARE 4 X 4 3/4'' DC ON PIPE RACKS &amp; MEASURE SAME, R/U FLOW LINE, WAIT ON CEMENT.</t>
+  </si>
+  <si>
+    <t>C181-65</t>
+  </si>
+  <si>
+    <t>APESCO#020</t>
+  </si>
+  <si>
+    <t>CONT RIH W/ 6 1/8\" BIT + 7\" SCR + X-OVER ON 186 JTS 3 1/2\" TBG TOTAL OF 206 JTS 3 1/2\" TBG F/DRK W/ S.L.M, P/U SINGLE, F/ BY PIPE RACKS (CLEAN+S.L.M &amp; DRIFT) ON 75 JTS 3 1/2\" TBG TOTAL OF 281 JTS 3 1/2 TBG IN HOLE TAG @ 8739', POOH W/ SAME L/D 1 JT ON TOTAL OF 160 JTS 3 1/2 TBG ON DRK - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>C41-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2023</t>
+  </si>
+  <si>
+    <t>H.P.J.S.M &amp; RIG SERVICE, CONT. POOH &amp; L/D DBP SETTING TOOL ON 181 TOT. OF 273 JTS 3 1/2\" TBG, RIH W/ 11 JTS 3 1/2” O.E TBG AS KILL STRING, LAND TBG HANGER, N/D BOPs &amp; N/UP W-H, P/T W-H VALVES T/500 PSI \"GOOD TEST\", R/D, MOVE LOADS OUT OF LOCATION, RIG RELEASE @ 18:00 HRS, 22 JULY 2026.</t>
+  </si>
+  <si>
+    <t>C109-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2024</t>
+  </si>
+  <si>
+    <t>H.P.J.S.M &amp; RIG SERVICE, KEEP WELL FLOWING TO STATION THROUGH 32/64\" FIXED CHOKE, ESP FREQ = 55Hz, WHP = 180 PSI &amp; FLP = 80 PSI, RIG DOWN &amp; RIG RELEASED @ 18:00 HRs.</t>
+  </si>
+  <si>
+    <t>C365-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2025</t>
+  </si>
+  <si>
+    <t>H.P.J.S.M &amp; RIG SERVICE, CONT. POOH W/ 6 1/8” TCI BIT + BHA ON 212 JTS, TOT. OF 252 JTS 3 1/2” TBG, CHK &amp; L/D BHA ''OK'', P/UP,M/UP &amp; ASSY + SERVICE PER. SLB ESP UNIT, PLUG IN POT HEAD CONN. RIH W/ PER. SLB ESP UNIT ON 110 JTS 3 1/2'' TBG, CHK CABLE &amp; TEST SENSOR EVERY 1000 Ft, P/T 3 1/2'' TBG, EVERY 40 JTS, T/ 500 PSI ''OK''.</t>
+  </si>
+  <si>
+    <t>C375-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2026</t>
+  </si>
+  <si>
+    <t>START R/M F/C189-65 &amp; R/UP ON C-375-65, 90% R/M &amp; 40% R/UP.</t>
+  </si>
+  <si>
+    <t>C233-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2028</t>
+  </si>
+  <si>
+    <t>CONT. R/M F/ C-245-65 &amp; R/UP ON C-233-65, 100% R/M &amp; 100% R/UP @ 16:30 HRs, SICP = 40 PSI &amp; SITP = 50 PSI, BLEED OFF PRESS. TO FLARE PIT, P/T W-H VALVEs &amp; 3 1/2\" TBG TO 500 PSI \" OK \".</t>
+  </si>
+  <si>
+    <t>C28-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2029</t>
+  </si>
+  <si>
+    <t>H.P.J.S.M &amp; RIG SERVICE, CONT. RIH W/ 6 1/8\" BIT + 1 JT 3 1/2\" TBG AS SPACE OUT + 7\" CSG SCR ON 40 JTS W/ SLM + 89 JTS F/ PIPE RACKS W/ CLEAN, DRIFT &amp; SLM, TOT. OF 280 JTS 3 1/2\" TBG, TAG FILL @ 8758' ( 25' OF FILL ), TRY TO PUSH DOWN &amp; CIRC. OUT FILL W/ NO PROGRESS ( HARD FILL ), POOH W/ 6 1/8\" BIT + 1 JT 3 1/2\" TBG AS SPACE OUT + 7\" CSG SCR ON 140 JTS TOT. OF 141 JTS 3 1/2\" TBG.</t>
+  </si>
+  <si>
+    <t>C169-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2033</t>
+  </si>
+  <si>
+    <t>CONT. R/UP ON C169-65, 97% R/UP.</t>
+  </si>
+  <si>
+    <t>C180-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2034</t>
+  </si>
+  <si>
+    <t>CONT. R/UP ON C180-65, 91% R/UP.</t>
+  </si>
+  <si>
+    <t>L59-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2035</t>
+  </si>
+  <si>
+    <t>CONT. R/UP ON L059-65, 85% R/UP.</t>
+  </si>
+  <si>
+    <t>C236-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2036</t>
+  </si>
+  <si>
+    <t>CONT. R/M F/SHAMS LIBYA MESSLA MAINBASE T/C236-65, 75% R/M &amp; 55% R/UP.</t>
+  </si>
+  <si>
+    <t>C376-65</t>
+  </si>
+  <si>
+    <t>SHAMS LY#W2037</t>
+  </si>
+  <si>
+    <t>H.P.J.S.M &amp; RIG SERVICE, CONT. DRILL OUT C.R F/8824.5 T/8825' (1 FT PROGRESS), GOT OIL RTN, STOP DRILLING, SWITCH RTN TO FLARE PIT &amp; CLOSE BOP, CONT. CIRC. UNTIL GOT WATER RTN, OPEN BOP &amp; SWITCH RTN BACK ON MUD SYSTEM, CONT. DRILL OUT CR F/8825' T/8826.5' (2.5 FT TOT. PROGRESS), CR DROPPED, CONT. PUSH DOWN CR TO BTM, TAG PBTD @8924', CIRC. &amp; SWEEP HOLE CLEAN W/15 BBLs HI-VIS PILL, R/D POWER SWIVEL, L/D 1 JT 3 1/2\" TBG, POOH W/6 1/8\" BIT + BHA ON 10 JTS 3 1/2\" TBG T/8610'.</t>
+  </si>
+  <si>
+    <t>C173-65</t>
+  </si>
+  <si>
+    <t>UWD#111</t>
+  </si>
+  <si>
+    <t>CONT POOH W/ 4.5\" SAND PUMP &amp; L/D 13 JTS 3 1/2\" EXCESS TBG TOTAL OF 38 JTS 3 1/2\" TBG &amp; CONT POOH W/ SAME ON 244 JTS X 3 1/2\" TBG &amp; L/D 4.5\" SAND PUMP (RECOVER 1 JT FULL OF SAND), RIH W/ 3 1/2\" C/V + B/V &amp; RIH W/ SAME ON 196 JTS 3 1/2\" TBG &amp; P/T TBG EVERY 1000' TO/ 750 PSI F/15 MIN (GOOD TEST) - INCOMPLETE.</t>
+  </si>
+  <si>
+    <t>C311-65</t>
+  </si>
+  <si>
+    <t>UWD#112</t>
+  </si>
+  <si>
+    <t>CONT RIH W/ C.V +B.V ON 88 JTS ON TOTAL 282 JTS 3 1/2'' TBG IN HOLE .P/T TO 750 PSI EVERY 1000' FOR 15 MINs - GOOD TEST, ATTEMPT TO DROP BAR NO SUCCESS &amp; POOH W/ CV+BV &amp; L/D 8 JTS EXCESS TBG ON RACKS, CONT POOH W/ SAME ON 142 JTS 3 1/2'' TBG ON DRK.</t>
+  </si>
+  <si>
+    <t>SINAWIN</t>
+  </si>
+  <si>
+    <t>G2-NC100</t>
+  </si>
+  <si>
+    <t>ILL#004</t>
+  </si>
+  <si>
+    <t>CONT RIH W/ ESP UNIT ON TOTAL 290 JTS 3 1/2\" TBG, MAKE CABLE SPLICE FOR LOWER PIGTAIL, LAND TBG HANGER W/ PUMP INTAKE @ 8545 FT, PREPARE TO N/D BOP &amp; N/UP WELL HEAD.</t>
+  </si>
+  <si>
+    <t>Sirte Oil Company</t>
+  </si>
+  <si>
+    <t>S.ZELTEN</t>
+  </si>
+  <si>
+    <t>C163-6</t>
+  </si>
+  <si>
+    <t>NWD#36</t>
+  </si>
+  <si>
+    <t>R/D 100%, R/M 100% &amp; R/U 0%, CONT LEVELING LOCATION. DISCONNECTING G/LINE AND PROD LINE IN PROGRESS.</t>
+  </si>
+  <si>
+    <t>S</t>
+  </si>
+  <si>
+    <t>SE.ZELTEN</t>
+  </si>
+  <si>
+    <t>C77-6</t>
+  </si>
+  <si>
+    <t>LORASCO #25</t>
+  </si>
+  <si>
+    <t>INFIELD MOBILIZATION RIG DOWN: 10%, RIG MOVE: 0%, RIG UP:0%, PREPARE RIG FOR CAT-III INSPECTION</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>N.ZELTEN</t>
+  </si>
+  <si>
+    <t>C179-6</t>
+  </si>
+  <si>
+    <t>ADWOC # 8</t>
+  </si>
+  <si>
+    <t>R/D 100%, R/M 100% &amp; R/U 95%, INSPECTION OF LIFTING EQUIPMENT, TRAVELING BLOCK AND FORKLIFT …ONGOING</t>
+  </si>
+  <si>
+    <t>W</t>
+  </si>
+  <si>
+    <t>JEBEL</t>
+  </si>
+  <si>
+    <t>P10-6</t>
+  </si>
+  <si>
+    <t>CHALL# 96</t>
+  </si>
+  <si>
+    <t>INFIELD MOBILIZATION. R/D :100%, R//M: 100%, R/U: 90%, WORK ON CLOSING NON-CONFORMITIES ITEMS, LIFTING GEAR AND TUBULAR INSPECTION IN PROGRESS.</t>
+  </si>
+  <si>
+    <t>O</t>
+  </si>
+  <si>
+    <t>C109-6</t>
+  </si>
+  <si>
+    <t>ADWOC# 5</t>
+  </si>
+  <si>
+    <t>INTERFIELD MOBILIZATION FROM RAGUBA TO ZELTEN. R/D: 100%, R/M: 100%, R/UP: 60%. PREPARE THE RIG FOR INSPECTION.</t>
+  </si>
+  <si>
+    <t>LEHIB</t>
+  </si>
+  <si>
+    <t>UU39-6</t>
+  </si>
+  <si>
+    <t>Q.B# 8</t>
+  </si>
+  <si>
+    <t>RIG UP: 100%. RIG ON PAYROLL AT 12:00 ON 25-JUL-2026, RECORD WHP = 0 PSI, BLEED OFF CSG PR F/ 1200 PSI TO ZERO, KILL WELL, FLOW CHECK - LEVEL STATIC, INSTALL BPV, N/D X-MASS TREE, N/U BOP’S, INSTALL RISER AND FLOW LINE.</t>
+  </si>
+  <si>
+    <t>C126-6</t>
+  </si>
+  <si>
+    <t>ADWOC#22</t>
+  </si>
+  <si>
+    <t>RIG DOWN: 100%, RIG MOVE: 100%, RIG UP: 85%, EIGER ENGINEERING OILFELD SERVICES COMPANY ON LOCATION FOR CAT-III RIG INSPECTION.</t>
+  </si>
+  <si>
+    <t>T</t>
+  </si>
+  <si>
+    <t>C108-6</t>
+  </si>
+  <si>
+    <t>NWD#53</t>
+  </si>
+  <si>
+    <t>CONTRIH W/ 2 3/8” TBG GAS-LIFT FINAL COMPLETION F/ 5380’ T/ 5495’ (W.E.G DEPTH), SET 5” R3 PKR AT 5476’, LAND TBG HGR, INSTALL BPV, N/D BOP’S, N/U X-MASS TREE &amp; P/TEST TO 1200 PSI OK, CONNECT GAS LINE TO WELLHEAD &amp; P/TEST T/ 1400 PSI OK, GAS LIFT WELL FOR CLEAN-UP TO FLARE PIT ON 64/64” CHK, WHP= 230 PSI, GAS INJ PR= 1180 PSI, WC= 96%, SAL= 30,000 PPM, CONT WELL CLEAN-UP.</t>
+  </si>
+  <si>
+    <t>WADI</t>
+  </si>
+  <si>
+    <t>D7-NC149</t>
+  </si>
+  <si>
+    <t>LAHEEB#1</t>
+  </si>
+  <si>
+    <t>R/U JOWFE POWER TONG, M/U 7” SHROUD, ASSMEBLE 7” ESP AND RIH ON 2 7/8” TBG FINAL COMPLETION T/ 4912’, CHECK CABLE CONDUCTIVITY AND P/TEST STRING T/ 1000 PSI EVERY 10 STD’S.</t>
+  </si>
+  <si>
+    <t>SEZELTEN</t>
+  </si>
+  <si>
+    <t>C236-6</t>
+  </si>
+  <si>
+    <t>FB#7</t>
+  </si>
+  <si>
+    <t>INTERFIELD MOBILIZATION. RIG DOWN:100%, RIG MOVE: 100%, RIG UP: 0%</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>RAGUBA</t>
+  </si>
+  <si>
+    <t>E56-20</t>
+  </si>
+  <si>
+    <t>NDD#4</t>
+  </si>
+  <si>
+    <t>CONT WASH DOWN SCALE F/ 1536’ T/ 1568’ (EXPECTED TOP FISH), CIRC &amp; SWEEP HOLE W/ HI-VIS PILL, POOH W/ 5 7/8” TAPER MILL TO SURF, M/U &amp; RIH W/ 5 7/8” WASHOVER SHOE F/ SURF T/ 1520’, WORK ON TIGHT SPOT @ R/TIME.</t>
   </si>
 </sst>
 </file>
@@ -527,7 +1094,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M2"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="true" style="9"/>
@@ -621,6 +1188,1928 @@
       </c>
       <c r="M2" s="15"/>
     </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B3" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="10">
+        <v>569</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="19"/>
+      <c r="I3" s="13">
+        <v>0</v>
+      </c>
+      <c r="J3" s="13">
+        <v>151335</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="10">
+        <v>569</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="13">
+        <v>0</v>
+      </c>
+      <c r="J4" s="13">
+        <v>1876120</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" s="17">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B5" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="10">
+        <v>569</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H5" s="19"/>
+      <c r="I5" s="13">
+        <v>0</v>
+      </c>
+      <c r="J5" s="13">
+        <v>476809</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="L5" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="10">
+        <v>569</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="19"/>
+      <c r="I6" s="13">
+        <v>0</v>
+      </c>
+      <c r="J6" s="13">
+        <v>5086575</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="L6" s="17">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B7" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="10">
+        <v>569</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="13">
+        <v>0</v>
+      </c>
+      <c r="J7" s="13">
+        <v>1086698</v>
+      </c>
+      <c r="K7" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="L7" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" s="10">
+        <v>569</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="13">
+        <v>0</v>
+      </c>
+      <c r="J8" s="13">
+        <v>2217691</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>38</v>
+      </c>
+      <c r="L8" s="17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B9" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="10">
+        <v>569</v>
+      </c>
+      <c r="D9" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G9" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="13">
+        <v>0</v>
+      </c>
+      <c r="J9" s="13">
+        <v>1709842</v>
+      </c>
+      <c r="K9" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="L9" s="17">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B10" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" s="10">
+        <v>569</v>
+      </c>
+      <c r="D10" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="13">
+        <v>0</v>
+      </c>
+      <c r="J10" s="13">
+        <v>22604</v>
+      </c>
+      <c r="K10" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="L10" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B11" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" s="10">
+        <v>569</v>
+      </c>
+      <c r="D11" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="F11" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="13">
+        <v>0</v>
+      </c>
+      <c r="J11" s="13">
+        <v>10662673</v>
+      </c>
+      <c r="K11" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="L11" s="17">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" s="10">
+        <v>569</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="G12" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="13">
+        <v>0</v>
+      </c>
+      <c r="J12" s="13">
+        <v>2865372</v>
+      </c>
+      <c r="K12" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="L12" s="17">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B13" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="10">
+        <v>569</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>55</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="13">
+        <v>0</v>
+      </c>
+      <c r="J13" s="13">
+        <v>571831</v>
+      </c>
+      <c r="K13" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="L13" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" s="10">
+        <v>569</v>
+      </c>
+      <c r="D14" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="13">
+        <v>0</v>
+      </c>
+      <c r="J14" s="13">
+        <v>2589357</v>
+      </c>
+      <c r="K14" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="17">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B15" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" s="10">
+        <v>569</v>
+      </c>
+      <c r="D15" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E15" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="13">
+        <v>0</v>
+      </c>
+      <c r="J15" s="13">
+        <v>0</v>
+      </c>
+      <c r="K15" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="L15" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" s="10">
+        <v>569</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>64</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="13">
+        <v>0</v>
+      </c>
+      <c r="J16" s="13">
+        <v>0</v>
+      </c>
+      <c r="K16" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B17" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" s="10">
+        <v>569</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>66</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>67</v>
+      </c>
+      <c r="G17" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="13">
+        <v>0</v>
+      </c>
+      <c r="J17" s="13">
+        <v>0</v>
+      </c>
+      <c r="K17" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="L17" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" s="10">
+        <v>569</v>
+      </c>
+      <c r="D18" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="E18" s="11" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" s="11" t="s">
+        <v>70</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H18" s="19"/>
+      <c r="I18" s="13">
+        <v>0</v>
+      </c>
+      <c r="J18" s="13">
+        <v>0</v>
+      </c>
+      <c r="K18" s="14" t="s">
+        <v>71</v>
+      </c>
+      <c r="L18" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B19" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" s="10">
+        <v>569</v>
+      </c>
+      <c r="D19" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="13">
+        <v>0</v>
+      </c>
+      <c r="J19" s="13">
+        <v>2310958</v>
+      </c>
+      <c r="K19" s="14" t="s">
+        <v>75</v>
+      </c>
+      <c r="L19" s="17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" s="10">
+        <v>569</v>
+      </c>
+      <c r="D20" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E20" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="F20" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G20" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="13">
+        <v>0</v>
+      </c>
+      <c r="J20" s="13">
+        <v>952112</v>
+      </c>
+      <c r="K20" s="14" t="s">
+        <v>78</v>
+      </c>
+      <c r="L20" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B21" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" s="10">
+        <v>569</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E21" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F21" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="13">
+        <v>0</v>
+      </c>
+      <c r="J21" s="13">
+        <v>356392</v>
+      </c>
+      <c r="K21" s="14" t="s">
+        <v>81</v>
+      </c>
+      <c r="L21" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" s="10">
+        <v>569</v>
+      </c>
+      <c r="D22" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E22" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="G22" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H22" s="19"/>
+      <c r="I22" s="13">
+        <v>0</v>
+      </c>
+      <c r="J22" s="13">
+        <v>9084335</v>
+      </c>
+      <c r="K22" s="14" t="s">
+        <v>84</v>
+      </c>
+      <c r="L22" s="17">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" s="10">
+        <v>569</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H23" s="19"/>
+      <c r="I23" s="13">
+        <v>0</v>
+      </c>
+      <c r="J23" s="13">
+        <v>5805277</v>
+      </c>
+      <c r="K23" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="L23" s="17">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="10">
+        <v>569</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="G24" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H24" s="19"/>
+      <c r="I24" s="13">
+        <v>0</v>
+      </c>
+      <c r="J24" s="13">
+        <v>495631</v>
+      </c>
+      <c r="K24" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="L24" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" s="10">
+        <v>569</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="G25" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="13">
+        <v>0</v>
+      </c>
+      <c r="J25" s="13">
+        <v>650459</v>
+      </c>
+      <c r="K25" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="L25" s="17">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
+      <c r="A26" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="10">
+        <v>569</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="G26" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="13">
+        <v>0</v>
+      </c>
+      <c r="J26" s="13">
+        <v>452201</v>
+      </c>
+      <c r="K26" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="L26" s="17">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
+      <c r="A27" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="10">
+        <v>569</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G27" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="19"/>
+      <c r="I27" s="13">
+        <v>0</v>
+      </c>
+      <c r="J27" s="13">
+        <v>778025</v>
+      </c>
+      <c r="K27" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="L27" s="17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
+      <c r="A28" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" s="10">
+        <v>569</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="13">
+        <v>0</v>
+      </c>
+      <c r="J28" s="13">
+        <v>1019913</v>
+      </c>
+      <c r="K28" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L28" s="17">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
+      <c r="A29" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" s="10">
+        <v>569</v>
+      </c>
+      <c r="D29" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E29" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="F29" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="G29" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="13">
+        <v>0</v>
+      </c>
+      <c r="J29" s="13">
+        <v>222404</v>
+      </c>
+      <c r="K29" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="L29" s="17">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" s="10">
+        <v>569</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E30" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="F30" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G30" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="19"/>
+      <c r="I30" s="13">
+        <v>0</v>
+      </c>
+      <c r="J30" s="13">
+        <v>2084397</v>
+      </c>
+      <c r="K30" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="L30" s="17">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" s="10">
+        <v>569</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="F31" s="11" t="s">
+        <v>112</v>
+      </c>
+      <c r="G31" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="13">
+        <v>0</v>
+      </c>
+      <c r="J31" s="13">
+        <v>194753</v>
+      </c>
+      <c r="K31" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="L31" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="A32" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="10">
+        <v>569</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="F32" s="11" t="s">
+        <v>115</v>
+      </c>
+      <c r="G32" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="13">
+        <v>0</v>
+      </c>
+      <c r="J32" s="13">
+        <v>0</v>
+      </c>
+      <c r="K32" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="L32" s="17">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
+      <c r="A33" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" s="10">
+        <v>569</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>117</v>
+      </c>
+      <c r="F33" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="G33" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="13">
+        <v>0</v>
+      </c>
+      <c r="J33" s="13">
+        <v>0</v>
+      </c>
+      <c r="K33" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="L33" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
+      <c r="A34" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" s="10">
+        <v>569</v>
+      </c>
+      <c r="D34" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E34" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="F34" s="11" t="s">
+        <v>121</v>
+      </c>
+      <c r="G34" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H34" s="19"/>
+      <c r="I34" s="13">
+        <v>0</v>
+      </c>
+      <c r="J34" s="13">
+        <v>0</v>
+      </c>
+      <c r="K34" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="L34" s="17">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
+      <c r="A35" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" s="10">
+        <v>569</v>
+      </c>
+      <c r="D35" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E35" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="F35" s="11" t="s">
+        <v>124</v>
+      </c>
+      <c r="G35" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="13">
+        <v>0</v>
+      </c>
+      <c r="J35" s="13">
+        <v>0</v>
+      </c>
+      <c r="K35" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="L35" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
+      <c r="A36" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="10">
+        <v>569</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>126</v>
+      </c>
+      <c r="F36" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="G36" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="13">
+        <v>0</v>
+      </c>
+      <c r="J36" s="13">
+        <v>0</v>
+      </c>
+      <c r="K36" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="L36" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
+      <c r="A37" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" s="10">
+        <v>569</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>129</v>
+      </c>
+      <c r="F37" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="19"/>
+      <c r="I37" s="13">
+        <v>0</v>
+      </c>
+      <c r="J37" s="13">
+        <v>0</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="L37" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
+      <c r="A38" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" s="10">
+        <v>569</v>
+      </c>
+      <c r="D38" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E38" s="11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F38" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="G38" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H38" s="19"/>
+      <c r="I38" s="13">
+        <v>0</v>
+      </c>
+      <c r="J38" s="13">
+        <v>0</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="L38" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
+      <c r="A39" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" s="10">
+        <v>569</v>
+      </c>
+      <c r="D39" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>135</v>
+      </c>
+      <c r="F39" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H39" s="19"/>
+      <c r="I39" s="13">
+        <v>0</v>
+      </c>
+      <c r="J39" s="13">
+        <v>0</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="L39" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
+      <c r="A40" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" s="10">
+        <v>569</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>138</v>
+      </c>
+      <c r="F40" s="11" t="s">
+        <v>139</v>
+      </c>
+      <c r="G40" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="13">
+        <v>0</v>
+      </c>
+      <c r="J40" s="13">
+        <v>0</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="L40" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
+      <c r="A41" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B41" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" s="10">
+        <v>569</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" s="11" t="s">
+        <v>142</v>
+      </c>
+      <c r="G41" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H41" s="19"/>
+      <c r="I41" s="13">
+        <v>0</v>
+      </c>
+      <c r="J41" s="13">
+        <v>0</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="L41" s="17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13">
+      <c r="A42" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" s="10">
+        <v>569</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="11" t="s">
+        <v>145</v>
+      </c>
+      <c r="G42" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="13">
+        <v>0</v>
+      </c>
+      <c r="J42" s="13">
+        <v>0</v>
+      </c>
+      <c r="K42" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="L42" s="17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13">
+      <c r="A43" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B43" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="10">
+        <v>569</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="F43" s="11" t="s">
+        <v>148</v>
+      </c>
+      <c r="G43" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="13">
+        <v>0</v>
+      </c>
+      <c r="J43" s="13">
+        <v>205534</v>
+      </c>
+      <c r="K43" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="L43" s="17">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13">
+      <c r="A44" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" s="10">
+        <v>569</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="11" t="s">
+        <v>150</v>
+      </c>
+      <c r="F44" s="11" t="s">
+        <v>151</v>
+      </c>
+      <c r="G44" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="H44" s="19"/>
+      <c r="I44" s="13">
+        <v>0</v>
+      </c>
+      <c r="J44" s="13">
+        <v>450243</v>
+      </c>
+      <c r="K44" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="L44" s="17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13">
+      <c r="A45" s="18">
+        <v>46226.0</v>
+      </c>
+      <c r="B45" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C45" s="10">
+        <v>569</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>154</v>
+      </c>
+      <c r="F45" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="G45" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="H45" s="19"/>
+      <c r="I45" s="13">
+        <v>0</v>
+      </c>
+      <c r="J45" s="13">
+        <v>4827851</v>
+      </c>
+      <c r="K45" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="L45" s="17">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13">
+      <c r="A46" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B46" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C46" s="10">
+        <v>572</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="F46" s="11" t="s">
+        <v>160</v>
+      </c>
+      <c r="G46" s="11"/>
+      <c r="H46" s="19"/>
+      <c r="I46" s="13">
+        <v>0</v>
+      </c>
+      <c r="J46" s="13">
+        <v>0</v>
+      </c>
+      <c r="K46" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="L46" s="17" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13">
+      <c r="A47" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B47" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C47" s="10">
+        <v>572</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="E47" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="F47" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="G47" s="11"/>
+      <c r="H47" s="19"/>
+      <c r="I47" s="13">
+        <v>0</v>
+      </c>
+      <c r="J47" s="13">
+        <v>0</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="L47" s="17" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13">
+      <c r="A48" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B48" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C48" s="10">
+        <v>572</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="F48" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="G48" s="11"/>
+      <c r="H48" s="19"/>
+      <c r="I48" s="13">
+        <v>0</v>
+      </c>
+      <c r="J48" s="13">
+        <v>0</v>
+      </c>
+      <c r="K48" s="14" t="s">
+        <v>171</v>
+      </c>
+      <c r="L48" s="17" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13">
+      <c r="A49" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B49" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C49" s="10">
+        <v>572</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>174</v>
+      </c>
+      <c r="F49" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="G49" s="11"/>
+      <c r="H49" s="19"/>
+      <c r="I49" s="13">
+        <v>0</v>
+      </c>
+      <c r="J49" s="13">
+        <v>0</v>
+      </c>
+      <c r="K49" s="14" t="s">
+        <v>176</v>
+      </c>
+      <c r="L49" s="17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13">
+      <c r="A50" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B50" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C50" s="10">
+        <v>572</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>178</v>
+      </c>
+      <c r="F50" s="11" t="s">
+        <v>179</v>
+      </c>
+      <c r="G50" s="11"/>
+      <c r="H50" s="19"/>
+      <c r="I50" s="13">
+        <v>0</v>
+      </c>
+      <c r="J50" s="13">
+        <v>0</v>
+      </c>
+      <c r="K50" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="L50" s="17" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13">
+      <c r="A51" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B51" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C51" s="10">
+        <v>572</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>181</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>182</v>
+      </c>
+      <c r="F51" s="11" t="s">
+        <v>183</v>
+      </c>
+      <c r="G51" s="11"/>
+      <c r="H51" s="19"/>
+      <c r="I51" s="13">
+        <v>0</v>
+      </c>
+      <c r="J51" s="13">
+        <v>0</v>
+      </c>
+      <c r="K51" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="L51" s="17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13">
+      <c r="A52" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B52" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="10">
+        <v>572</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>185</v>
+      </c>
+      <c r="F52" s="11" t="s">
+        <v>186</v>
+      </c>
+      <c r="G52" s="11"/>
+      <c r="H52" s="19"/>
+      <c r="I52" s="13">
+        <v>0</v>
+      </c>
+      <c r="J52" s="13">
+        <v>0</v>
+      </c>
+      <c r="K52" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="L52" s="17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13">
+      <c r="A53" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C53" s="10">
+        <v>572</v>
+      </c>
+      <c r="D53" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="E53" s="11" t="s">
+        <v>189</v>
+      </c>
+      <c r="F53" s="11" t="s">
+        <v>190</v>
+      </c>
+      <c r="G53" s="11"/>
+      <c r="H53" s="19"/>
+      <c r="I53" s="13">
+        <v>0</v>
+      </c>
+      <c r="J53" s="13">
+        <v>0</v>
+      </c>
+      <c r="K53" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="L53" s="17">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13">
+      <c r="A54" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C54" s="10">
+        <v>572</v>
+      </c>
+      <c r="D54" s="11" t="s">
+        <v>192</v>
+      </c>
+      <c r="E54" s="11" t="s">
+        <v>193</v>
+      </c>
+      <c r="F54" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="G54" s="11"/>
+      <c r="H54" s="19"/>
+      <c r="I54" s="13">
+        <v>0</v>
+      </c>
+      <c r="J54" s="13">
+        <v>0</v>
+      </c>
+      <c r="K54" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="L54" s="17">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13">
+      <c r="A55" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B55" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C55" s="10">
+        <v>572</v>
+      </c>
+      <c r="D55" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="E55" s="11" t="s">
+        <v>197</v>
+      </c>
+      <c r="F55" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="G55" s="11"/>
+      <c r="H55" s="19"/>
+      <c r="I55" s="13">
+        <v>0</v>
+      </c>
+      <c r="J55" s="13">
+        <v>0</v>
+      </c>
+      <c r="K55" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="L55" s="17" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13">
+      <c r="A56" s="18">
+        <v>46229.0</v>
+      </c>
+      <c r="B56" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C56" s="10">
+        <v>572</v>
+      </c>
+      <c r="D56" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="E56" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="F56" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="G56" s="11"/>
+      <c r="H56" s="19"/>
+      <c r="I56" s="13">
+        <v>0</v>
+      </c>
+      <c r="J56" s="13">
+        <v>0</v>
+      </c>
+      <c r="K56" s="14" t="s">
+        <v>204</v>
+      </c>
+      <c r="L56" s="17">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
